--- a/EXCEL/Homework/IF statement Exercise Questions(SAYAR PAUL).xlsx
+++ b/EXCEL/Homework/IF statement Exercise Questions(SAYAR PAUL).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANUDIP_BY_SAYAR_DPBA\EXCEL\Homework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CD690F9-76F5-4943-9FFD-E2670D602D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA38983A-1162-4027-8EAB-84C37D09711B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2ABEEB38-1789-494D-ACEA-A194A550D6D8}"/>
   </bookViews>
@@ -122,7 +122,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,15 +131,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +165,54 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -180,13 +244,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,413 +599,428 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0057EBA8-F5A3-4CB0-BF66-0B049AD813E5}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="77" customWidth="1"/>
-    <col min="7" max="7" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="55.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="O1" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>101</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>120</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>150</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="str">
+      <c r="F2" s="4" t="str">
         <f>IF(C2&gt;=D2,"MET","NOT MET")</f>
         <v>NOT MET</v>
       </c>
-      <c r="G2" s="3" t="str">
+      <c r="G2" s="5" t="str">
         <f>IF(AND(E2="North",C2&gt;200),"Eligible","Not Eligible")</f>
         <v>Not Eligible</v>
       </c>
-      <c r="H2" s="3" t="str">
+      <c r="H2" s="6" t="str">
         <f>IF(C2&gt;=200,"10%",IF(C2&gt;=150,"7%","5%"))</f>
         <v>5%</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="7">
         <f>IF(C2&gt;=D2,C2*10%,C2*5%)</f>
         <v>6</v>
       </c>
-      <c r="J2" s="3" t="str">
+      <c r="J2" s="8" t="str">
         <f>IF(C2&gt;=200,"Excellent",IF(C2&gt;=150,"Good","Needs Improvement"))</f>
         <v>Needs Improvement</v>
       </c>
-      <c r="K2" s="3" t="str">
+      <c r="K2" s="9" t="str">
         <f>IF(C2&gt;200,"High",IF(C2&gt;=100,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="10">
         <f>IF(AND(C2&gt;=150,E2="North"),500,300)</f>
         <v>300</v>
       </c>
-      <c r="M2" s="3" t="str">
+      <c r="M2" s="11" t="str">
         <f>IF(C2&gt;=PERCENTILE($C$2:$C$7,0.75),"High Performer","Low Performer")</f>
         <v>Low Performer</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="O2" s="12"/>
+    </row>
+    <row r="3" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>102</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>150</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>140</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="str">
+      <c r="F3" s="4" t="str">
         <f t="shared" ref="F3:F7" si="0">IF(C3&gt;=D3,"MET","NOT MET")</f>
         <v>MET</v>
       </c>
-      <c r="G3" s="3" t="str">
+      <c r="G3" s="5" t="str">
         <f t="shared" ref="G3:G7" si="1">IF(AND(E3="North",C3&gt;200),"Eligible","Not Eligible")</f>
         <v>Not Eligible</v>
       </c>
-      <c r="H3" s="3" t="str">
+      <c r="H3" s="6" t="str">
         <f t="shared" ref="H3:H7" si="2">IF(C3&gt;=200,"10%",IF(C3&gt;=150,"7%","5%"))</f>
         <v>7%</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="7">
         <f t="shared" ref="I3:I7" si="3">IF(C3&gt;=D3,C3*10%,C3*5%)</f>
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="str">
+      <c r="J3" s="8" t="str">
         <f t="shared" ref="J3:J7" si="4">IF(C3&gt;=200,"Excellent",IF(C3&gt;=150,"Good","Needs Improvement"))</f>
         <v>Good</v>
       </c>
-      <c r="K3" s="3" t="str">
+      <c r="K3" s="9" t="str">
         <f t="shared" ref="K3:K7" si="5">IF(C3&gt;200,"High",IF(C3&gt;=100,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="10">
         <f t="shared" ref="L3:L7" si="6">IF(AND(C3&gt;=150,E3="North"),500,300)</f>
         <v>300</v>
       </c>
-      <c r="M3" s="3" t="str">
+      <c r="M3" s="11" t="str">
         <f t="shared" ref="M3:M7" si="7">IF(C3&gt;=PERCENTILE($C$2:$C$7,0.75),"High Performer","Low Performer")</f>
         <v>Low Performer</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="O3" s="12"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>103</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>200</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>200</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3" t="str">
+      <c r="F4" s="4" t="str">
         <f t="shared" si="0"/>
         <v>MET</v>
       </c>
-      <c r="G4" s="3" t="str">
+      <c r="G4" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Not Eligible</v>
       </c>
-      <c r="H4" s="3" t="str">
+      <c r="H4" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10%</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="7">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="J4" s="3" t="str">
+      <c r="J4" s="8" t="str">
         <f t="shared" si="4"/>
         <v>Excellent</v>
       </c>
-      <c r="K4" s="3" t="str">
+      <c r="K4" s="9" t="str">
         <f t="shared" si="5"/>
         <v>Medium</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="10">
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
-      <c r="M4" s="3" t="str">
+      <c r="M4" s="11" t="str">
         <f t="shared" si="7"/>
         <v>High Performer</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="O4" s="12"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>104</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>90</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>100</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="3" t="str">
+      <c r="F5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NOT MET</v>
       </c>
-      <c r="G5" s="3" t="str">
+      <c r="G5" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Not Eligible</v>
       </c>
-      <c r="H5" s="3" t="str">
+      <c r="H5" s="6" t="str">
         <f t="shared" si="2"/>
         <v>5%</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="7">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="J5" s="3" t="str">
+      <c r="J5" s="8" t="str">
         <f t="shared" si="4"/>
         <v>Needs Improvement</v>
       </c>
-      <c r="K5" s="3" t="str">
+      <c r="K5" s="9" t="str">
         <f t="shared" si="5"/>
         <v>Low</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="10">
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
-      <c r="M5" s="3" t="str">
+      <c r="M5" s="11" t="str">
         <f t="shared" si="7"/>
         <v>Low Performer</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>105</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>220</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>210</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="3" t="str">
+      <c r="F6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>MET</v>
       </c>
-      <c r="G6" s="3" t="str">
+      <c r="G6" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Eligible</v>
       </c>
-      <c r="H6" s="3" t="str">
+      <c r="H6" s="6" t="str">
         <f t="shared" si="2"/>
         <v>10%</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="7">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="J6" s="3" t="str">
+      <c r="J6" s="8" t="str">
         <f t="shared" si="4"/>
         <v>Excellent</v>
       </c>
-      <c r="K6" s="3" t="str">
+      <c r="K6" s="9" t="str">
         <f t="shared" si="5"/>
         <v>High</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="10">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="M6" s="3" t="str">
+      <c r="M6" s="11" t="str">
         <f t="shared" si="7"/>
         <v>High Performer</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="O6" s="12"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>106</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>130</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>160</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="3" t="str">
+      <c r="F7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>NOT MET</v>
       </c>
-      <c r="G7" s="3" t="str">
+      <c r="G7" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Not Eligible</v>
       </c>
-      <c r="H7" s="3" t="str">
+      <c r="H7" s="6" t="str">
         <f t="shared" si="2"/>
         <v>5%</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="7">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="J7" s="3" t="str">
+      <c r="J7" s="8" t="str">
         <f t="shared" si="4"/>
         <v>Needs Improvement</v>
       </c>
-      <c r="K7" s="3" t="str">
+      <c r="K7" s="9" t="str">
         <f t="shared" si="5"/>
         <v>Medium</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="10">
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
-      <c r="M7" s="3" t="str">
+      <c r="M7" s="11" t="str">
         <f t="shared" si="7"/>
         <v>Low Performer</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F27" s="4"/>
+      <c r="O7" s="12"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O8" s="12"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O9" s="12"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O10" s="12"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O11" s="12"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O12" s="12"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O13" s="12"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O14" s="12"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O16" s="12"/>
+    </row>
+    <row r="17" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O17" s="12"/>
+    </row>
+    <row r="18" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O18" s="12"/>
+    </row>
+    <row r="19" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O19" s="12"/>
+    </row>
+    <row r="20" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O20" s="12"/>
+    </row>
+    <row r="21" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O21" s="12"/>
+    </row>
+    <row r="22" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O22" s="1"/>
+    </row>
+    <row r="23" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O23" s="1"/>
+    </row>
+    <row r="24" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O24" s="1"/>
+    </row>
+    <row r="25" spans="15:15" x14ac:dyDescent="0.3">
+      <c r="O25" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F12:F27"/>
+    <mergeCell ref="O1:O21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/EXCEL/Homework/IF statement Exercise Questions(SAYAR PAUL).xlsx
+++ b/EXCEL/Homework/IF statement Exercise Questions(SAYAR PAUL).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANUDIP_BY_SAYAR_DPBA\EXCEL\Homework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA38983A-1162-4027-8EAB-84C37D09711B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FE04A9-31CB-4199-A69E-2F8196992802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2ABEEB38-1789-494D-ACEA-A194A550D6D8}"/>
   </bookViews>
@@ -279,11 +279,11 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,7 +640,7 @@
       <c r="G1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -658,7 +658,7 @@
       <c r="M1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="13" t="s">
         <v>23</v>
       </c>
     </row>
@@ -707,10 +707,10 @@
         <v>300</v>
       </c>
       <c r="M2" s="11" t="str">
-        <f>IF(C2&gt;=PERCENTILE($C$2:$C$7,0.75),"High Performer","Low Performer")</f>
+        <f t="shared" ref="M2:M7" si="0">IF(C2&gt;=PERCENTILE($C$2:$C$7,0.75),"High Performer","Low Performer")</f>
         <v>Low Performer</v>
       </c>
-      <c r="O2" s="12"/>
+      <c r="O2" s="13"/>
     </row>
     <row r="3" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
@@ -729,38 +729,38 @@
         <v>12</v>
       </c>
       <c r="F3" s="4" t="str">
-        <f t="shared" ref="F3:F7" si="0">IF(C3&gt;=D3,"MET","NOT MET")</f>
+        <f t="shared" ref="F3:F7" si="1">IF(C3&gt;=D3,"MET","NOT MET")</f>
         <v>MET</v>
       </c>
       <c r="G3" s="5" t="str">
-        <f t="shared" ref="G3:G7" si="1">IF(AND(E3="North",C3&gt;200),"Eligible","Not Eligible")</f>
+        <f t="shared" ref="G3:G7" si="2">IF(AND(E3="North",C3&gt;200),"Eligible","Not Eligible")</f>
         <v>Not Eligible</v>
       </c>
       <c r="H3" s="6" t="str">
-        <f t="shared" ref="H3:H7" si="2">IF(C3&gt;=200,"10%",IF(C3&gt;=150,"7%","5%"))</f>
+        <f t="shared" ref="H3:H7" si="3">IF(C3&gt;=200,"10%",IF(C3&gt;=150,"7%","5%"))</f>
         <v>7%</v>
       </c>
       <c r="I3" s="7">
-        <f t="shared" ref="I3:I7" si="3">IF(C3&gt;=D3,C3*10%,C3*5%)</f>
+        <f t="shared" ref="I3:I7" si="4">IF(C3&gt;=D3,C3*10%,C3*5%)</f>
         <v>15</v>
       </c>
       <c r="J3" s="8" t="str">
-        <f t="shared" ref="J3:J7" si="4">IF(C3&gt;=200,"Excellent",IF(C3&gt;=150,"Good","Needs Improvement"))</f>
+        <f t="shared" ref="J3:J7" si="5">IF(C3&gt;=200,"Excellent",IF(C3&gt;=150,"Good","Needs Improvement"))</f>
         <v>Good</v>
       </c>
       <c r="K3" s="9" t="str">
-        <f t="shared" ref="K3:K7" si="5">IF(C3&gt;200,"High",IF(C3&gt;=100,"Medium","Low"))</f>
+        <f t="shared" ref="K3:K7" si="6">IF(C3&gt;200,"High",IF(C3&gt;=100,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
       <c r="L3" s="10">
-        <f t="shared" ref="L3:L7" si="6">IF(AND(C3&gt;=150,E3="North"),500,300)</f>
+        <f t="shared" ref="L3:L7" si="7">IF(AND(C3&gt;=150,E3="North"),500,300)</f>
         <v>300</v>
       </c>
       <c r="M3" s="11" t="str">
-        <f t="shared" ref="M3:M7" si="7">IF(C3&gt;=PERCENTILE($C$2:$C$7,0.75),"High Performer","Low Performer")</f>
+        <f t="shared" si="0"/>
         <v>Low Performer</v>
       </c>
-      <c r="O3" s="12"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
@@ -779,38 +779,38 @@
         <v>13</v>
       </c>
       <c r="F4" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>MET</v>
+      </c>
+      <c r="G4" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="H4" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>10%</v>
+      </c>
+      <c r="I4" s="7">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="J4" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Excellent</v>
+      </c>
+      <c r="K4" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>Medium</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>MET</v>
-      </c>
-      <c r="G4" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Eligible</v>
-      </c>
-      <c r="H4" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10%</v>
-      </c>
-      <c r="I4" s="7">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="J4" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Excellent</v>
-      </c>
-      <c r="K4" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium</v>
-      </c>
-      <c r="L4" s="10">
-        <f t="shared" si="6"/>
-        <v>300</v>
-      </c>
-      <c r="M4" s="11" t="str">
-        <f t="shared" si="7"/>
         <v>High Performer</v>
       </c>
-      <c r="O4" s="12"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
@@ -829,38 +829,38 @@
         <v>14</v>
       </c>
       <c r="F5" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>NOT MET</v>
+      </c>
+      <c r="G5" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="H5" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>5%</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="4"/>
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="K5" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>Low</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M5" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>NOT MET</v>
-      </c>
-      <c r="G5" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Eligible</v>
-      </c>
-      <c r="H5" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>5%</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="3"/>
-        <v>4.5</v>
-      </c>
-      <c r="J5" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Needs Improvement</v>
-      </c>
-      <c r="K5" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Low</v>
-      </c>
-      <c r="L5" s="10">
-        <f t="shared" si="6"/>
-        <v>300</v>
-      </c>
-      <c r="M5" s="11" t="str">
-        <f t="shared" si="7"/>
         <v>Low Performer</v>
       </c>
-      <c r="O5" s="12"/>
+      <c r="O5" s="13"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
@@ -879,38 +879,38 @@
         <v>11</v>
       </c>
       <c r="F6" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>MET</v>
+      </c>
+      <c r="G6" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Eligible</v>
+      </c>
+      <c r="H6" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>10%</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="J6" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Excellent</v>
+      </c>
+      <c r="K6" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>High</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="M6" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>MET</v>
-      </c>
-      <c r="G6" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Eligible</v>
-      </c>
-      <c r="H6" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>10%</v>
-      </c>
-      <c r="I6" s="7">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="J6" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Excellent</v>
-      </c>
-      <c r="K6" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>High</v>
-      </c>
-      <c r="L6" s="10">
-        <f t="shared" si="6"/>
-        <v>500</v>
-      </c>
-      <c r="M6" s="11" t="str">
-        <f t="shared" si="7"/>
         <v>High Performer</v>
       </c>
-      <c r="O6" s="12"/>
+      <c r="O6" s="13"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
@@ -929,80 +929,80 @@
         <v>12</v>
       </c>
       <c r="F7" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>NOT MET</v>
+      </c>
+      <c r="G7" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="H7" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>5%</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="4"/>
+        <v>6.5</v>
+      </c>
+      <c r="J7" s="8" t="str">
+        <f t="shared" si="5"/>
+        <v>Needs Improvement</v>
+      </c>
+      <c r="K7" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>Medium</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M7" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>NOT MET</v>
-      </c>
-      <c r="G7" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>Not Eligible</v>
-      </c>
-      <c r="H7" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>5%</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" si="3"/>
-        <v>6.5</v>
-      </c>
-      <c r="J7" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>Needs Improvement</v>
-      </c>
-      <c r="K7" s="9" t="str">
-        <f t="shared" si="5"/>
-        <v>Medium</v>
-      </c>
-      <c r="L7" s="10">
-        <f t="shared" si="6"/>
-        <v>300</v>
-      </c>
-      <c r="M7" s="11" t="str">
-        <f t="shared" si="7"/>
         <v>Low Performer</v>
       </c>
-      <c r="O7" s="12"/>
+      <c r="O7" s="13"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O8" s="12"/>
+      <c r="O8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O9" s="12"/>
+      <c r="O9" s="13"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O10" s="12"/>
+      <c r="O10" s="13"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O11" s="12"/>
+      <c r="O11" s="13"/>
     </row>
     <row r="12" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="O12" s="12"/>
+      <c r="O12" s="13"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O13" s="12"/>
+      <c r="O13" s="13"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O14" s="12"/>
+      <c r="O14" s="13"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O15" s="12"/>
+      <c r="O15" s="13"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O16" s="12"/>
+      <c r="O16" s="13"/>
     </row>
     <row r="17" spans="15:15" x14ac:dyDescent="0.3">
-      <c r="O17" s="12"/>
+      <c r="O17" s="13"/>
     </row>
     <row r="18" spans="15:15" x14ac:dyDescent="0.3">
-      <c r="O18" s="12"/>
+      <c r="O18" s="13"/>
     </row>
     <row r="19" spans="15:15" x14ac:dyDescent="0.3">
-      <c r="O19" s="12"/>
+      <c r="O19" s="13"/>
     </row>
     <row r="20" spans="15:15" x14ac:dyDescent="0.3">
-      <c r="O20" s="12"/>
+      <c r="O20" s="13"/>
     </row>
     <row r="21" spans="15:15" x14ac:dyDescent="0.3">
-      <c r="O21" s="12"/>
+      <c r="O21" s="13"/>
     </row>
     <row r="22" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O22" s="1"/>
